--- a/demo-excel/08-Target-Komisi-Sales-demo.xlsx
+++ b/demo-excel/08-Target-Komisi-Sales-demo.xlsx
@@ -348,7 +348,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Target vs Realisasi per Sales (Rp)</a:t>
+              <a:t>Target vs Realisasi per Sales (Rp juta)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -367,7 +367,13 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0EA5A4"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0EA5A4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -391,7 +397,13 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2563EB"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="2563EB"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -415,6 +427,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -426,15 +439,26 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E3E8F1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0,," sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -451,7 +475,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3060000"/>
+    <ext cx="5760000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>

--- a/demo-excel/08-Target-Komisi-Sales-demo.xlsx
+++ b/demo-excel/08-Target-Komisi-Sales-demo.xlsx
@@ -12,9 +12,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SALES" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PENJUALAN" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOMISI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-REKAP_TAHUNAN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-SLIP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-DASHBOARD" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PENJUALAN'!$A$5:$D$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PENJUALAN'!$A$5:$D$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +33,7 @@
     <numFmt numFmtId="168" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +116,29 @@
       <color rgb="005B6B82"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B1A30"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0033445C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -173,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -242,6 +268,12 @@
     <xf numFmtId="168" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -919,7 +951,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Catatan penjualan (kapasitas 300 baris): tanggal, sales, jenis, nilai.</t>
+          <t>Catatan penjualan (kapasitas 120 baris): tanggal, sales, jenis, nilai.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D305"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1370,7 +1402,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Kapasitas 300 baris</t>
+          <t>Kapasitas 120 baris</t>
         </is>
       </c>
     </row>
@@ -3107,1094 +3139,14 @@
       <c r="C125" s="24" t="n"/>
       <c r="D125" s="25" t="n"/>
     </row>
-    <row r="126">
-      <c r="A126" s="26" t="n"/>
-      <c r="B126" s="24" t="n"/>
-      <c r="C126" s="24" t="n"/>
-      <c r="D126" s="25" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="26" t="n"/>
-      <c r="B127" s="24" t="n"/>
-      <c r="C127" s="24" t="n"/>
-      <c r="D127" s="25" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="26" t="n"/>
-      <c r="B128" s="24" t="n"/>
-      <c r="C128" s="24" t="n"/>
-      <c r="D128" s="25" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="26" t="n"/>
-      <c r="B129" s="24" t="n"/>
-      <c r="C129" s="24" t="n"/>
-      <c r="D129" s="25" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="26" t="n"/>
-      <c r="B130" s="24" t="n"/>
-      <c r="C130" s="24" t="n"/>
-      <c r="D130" s="25" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="26" t="n"/>
-      <c r="B131" s="24" t="n"/>
-      <c r="C131" s="24" t="n"/>
-      <c r="D131" s="25" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="26" t="n"/>
-      <c r="B132" s="24" t="n"/>
-      <c r="C132" s="24" t="n"/>
-      <c r="D132" s="25" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="26" t="n"/>
-      <c r="B133" s="24" t="n"/>
-      <c r="C133" s="24" t="n"/>
-      <c r="D133" s="25" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="26" t="n"/>
-      <c r="B134" s="24" t="n"/>
-      <c r="C134" s="24" t="n"/>
-      <c r="D134" s="25" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="26" t="n"/>
-      <c r="B135" s="24" t="n"/>
-      <c r="C135" s="24" t="n"/>
-      <c r="D135" s="25" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="26" t="n"/>
-      <c r="B136" s="24" t="n"/>
-      <c r="C136" s="24" t="n"/>
-      <c r="D136" s="25" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="26" t="n"/>
-      <c r="B137" s="24" t="n"/>
-      <c r="C137" s="24" t="n"/>
-      <c r="D137" s="25" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="26" t="n"/>
-      <c r="B138" s="24" t="n"/>
-      <c r="C138" s="24" t="n"/>
-      <c r="D138" s="25" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="26" t="n"/>
-      <c r="B139" s="24" t="n"/>
-      <c r="C139" s="24" t="n"/>
-      <c r="D139" s="25" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="26" t="n"/>
-      <c r="B140" s="24" t="n"/>
-      <c r="C140" s="24" t="n"/>
-      <c r="D140" s="25" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="26" t="n"/>
-      <c r="B141" s="24" t="n"/>
-      <c r="C141" s="24" t="n"/>
-      <c r="D141" s="25" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="26" t="n"/>
-      <c r="B142" s="24" t="n"/>
-      <c r="C142" s="24" t="n"/>
-      <c r="D142" s="25" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="26" t="n"/>
-      <c r="B143" s="24" t="n"/>
-      <c r="C143" s="24" t="n"/>
-      <c r="D143" s="25" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="26" t="n"/>
-      <c r="B144" s="24" t="n"/>
-      <c r="C144" s="24" t="n"/>
-      <c r="D144" s="25" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="26" t="n"/>
-      <c r="B145" s="24" t="n"/>
-      <c r="C145" s="24" t="n"/>
-      <c r="D145" s="25" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="26" t="n"/>
-      <c r="B146" s="24" t="n"/>
-      <c r="C146" s="24" t="n"/>
-      <c r="D146" s="25" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="26" t="n"/>
-      <c r="B147" s="24" t="n"/>
-      <c r="C147" s="24" t="n"/>
-      <c r="D147" s="25" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="26" t="n"/>
-      <c r="B148" s="24" t="n"/>
-      <c r="C148" s="24" t="n"/>
-      <c r="D148" s="25" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="26" t="n"/>
-      <c r="B149" s="24" t="n"/>
-      <c r="C149" s="24" t="n"/>
-      <c r="D149" s="25" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="26" t="n"/>
-      <c r="B150" s="24" t="n"/>
-      <c r="C150" s="24" t="n"/>
-      <c r="D150" s="25" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="26" t="n"/>
-      <c r="B151" s="24" t="n"/>
-      <c r="C151" s="24" t="n"/>
-      <c r="D151" s="25" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="26" t="n"/>
-      <c r="B152" s="24" t="n"/>
-      <c r="C152" s="24" t="n"/>
-      <c r="D152" s="25" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="26" t="n"/>
-      <c r="B153" s="24" t="n"/>
-      <c r="C153" s="24" t="n"/>
-      <c r="D153" s="25" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="26" t="n"/>
-      <c r="B154" s="24" t="n"/>
-      <c r="C154" s="24" t="n"/>
-      <c r="D154" s="25" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="26" t="n"/>
-      <c r="B155" s="24" t="n"/>
-      <c r="C155" s="24" t="n"/>
-      <c r="D155" s="25" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="26" t="n"/>
-      <c r="B156" s="24" t="n"/>
-      <c r="C156" s="24" t="n"/>
-      <c r="D156" s="25" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="26" t="n"/>
-      <c r="B157" s="24" t="n"/>
-      <c r="C157" s="24" t="n"/>
-      <c r="D157" s="25" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="26" t="n"/>
-      <c r="B158" s="24" t="n"/>
-      <c r="C158" s="24" t="n"/>
-      <c r="D158" s="25" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="26" t="n"/>
-      <c r="B159" s="24" t="n"/>
-      <c r="C159" s="24" t="n"/>
-      <c r="D159" s="25" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="26" t="n"/>
-      <c r="B160" s="24" t="n"/>
-      <c r="C160" s="24" t="n"/>
-      <c r="D160" s="25" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="26" t="n"/>
-      <c r="B161" s="24" t="n"/>
-      <c r="C161" s="24" t="n"/>
-      <c r="D161" s="25" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="26" t="n"/>
-      <c r="B162" s="24" t="n"/>
-      <c r="C162" s="24" t="n"/>
-      <c r="D162" s="25" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="26" t="n"/>
-      <c r="B163" s="24" t="n"/>
-      <c r="C163" s="24" t="n"/>
-      <c r="D163" s="25" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="26" t="n"/>
-      <c r="B164" s="24" t="n"/>
-      <c r="C164" s="24" t="n"/>
-      <c r="D164" s="25" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="26" t="n"/>
-      <c r="B165" s="24" t="n"/>
-      <c r="C165" s="24" t="n"/>
-      <c r="D165" s="25" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="26" t="n"/>
-      <c r="B166" s="24" t="n"/>
-      <c r="C166" s="24" t="n"/>
-      <c r="D166" s="25" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="26" t="n"/>
-      <c r="B167" s="24" t="n"/>
-      <c r="C167" s="24" t="n"/>
-      <c r="D167" s="25" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="26" t="n"/>
-      <c r="B168" s="24" t="n"/>
-      <c r="C168" s="24" t="n"/>
-      <c r="D168" s="25" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="26" t="n"/>
-      <c r="B169" s="24" t="n"/>
-      <c r="C169" s="24" t="n"/>
-      <c r="D169" s="25" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="26" t="n"/>
-      <c r="B170" s="24" t="n"/>
-      <c r="C170" s="24" t="n"/>
-      <c r="D170" s="25" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="26" t="n"/>
-      <c r="B171" s="24" t="n"/>
-      <c r="C171" s="24" t="n"/>
-      <c r="D171" s="25" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="26" t="n"/>
-      <c r="B172" s="24" t="n"/>
-      <c r="C172" s="24" t="n"/>
-      <c r="D172" s="25" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="26" t="n"/>
-      <c r="B173" s="24" t="n"/>
-      <c r="C173" s="24" t="n"/>
-      <c r="D173" s="25" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="26" t="n"/>
-      <c r="B174" s="24" t="n"/>
-      <c r="C174" s="24" t="n"/>
-      <c r="D174" s="25" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="26" t="n"/>
-      <c r="B175" s="24" t="n"/>
-      <c r="C175" s="24" t="n"/>
-      <c r="D175" s="25" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="26" t="n"/>
-      <c r="B176" s="24" t="n"/>
-      <c r="C176" s="24" t="n"/>
-      <c r="D176" s="25" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="26" t="n"/>
-      <c r="B177" s="24" t="n"/>
-      <c r="C177" s="24" t="n"/>
-      <c r="D177" s="25" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="26" t="n"/>
-      <c r="B178" s="24" t="n"/>
-      <c r="C178" s="24" t="n"/>
-      <c r="D178" s="25" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="26" t="n"/>
-      <c r="B179" s="24" t="n"/>
-      <c r="C179" s="24" t="n"/>
-      <c r="D179" s="25" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="26" t="n"/>
-      <c r="B180" s="24" t="n"/>
-      <c r="C180" s="24" t="n"/>
-      <c r="D180" s="25" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="26" t="n"/>
-      <c r="B181" s="24" t="n"/>
-      <c r="C181" s="24" t="n"/>
-      <c r="D181" s="25" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="26" t="n"/>
-      <c r="B182" s="24" t="n"/>
-      <c r="C182" s="24" t="n"/>
-      <c r="D182" s="25" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="26" t="n"/>
-      <c r="B183" s="24" t="n"/>
-      <c r="C183" s="24" t="n"/>
-      <c r="D183" s="25" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="26" t="n"/>
-      <c r="B184" s="24" t="n"/>
-      <c r="C184" s="24" t="n"/>
-      <c r="D184" s="25" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="26" t="n"/>
-      <c r="B185" s="24" t="n"/>
-      <c r="C185" s="24" t="n"/>
-      <c r="D185" s="25" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="26" t="n"/>
-      <c r="B186" s="24" t="n"/>
-      <c r="C186" s="24" t="n"/>
-      <c r="D186" s="25" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="26" t="n"/>
-      <c r="B187" s="24" t="n"/>
-      <c r="C187" s="24" t="n"/>
-      <c r="D187" s="25" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="26" t="n"/>
-      <c r="B188" s="24" t="n"/>
-      <c r="C188" s="24" t="n"/>
-      <c r="D188" s="25" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="26" t="n"/>
-      <c r="B189" s="24" t="n"/>
-      <c r="C189" s="24" t="n"/>
-      <c r="D189" s="25" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="26" t="n"/>
-      <c r="B190" s="24" t="n"/>
-      <c r="C190" s="24" t="n"/>
-      <c r="D190" s="25" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="26" t="n"/>
-      <c r="B191" s="24" t="n"/>
-      <c r="C191" s="24" t="n"/>
-      <c r="D191" s="25" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="26" t="n"/>
-      <c r="B192" s="24" t="n"/>
-      <c r="C192" s="24" t="n"/>
-      <c r="D192" s="25" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="26" t="n"/>
-      <c r="B193" s="24" t="n"/>
-      <c r="C193" s="24" t="n"/>
-      <c r="D193" s="25" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="26" t="n"/>
-      <c r="B194" s="24" t="n"/>
-      <c r="C194" s="24" t="n"/>
-      <c r="D194" s="25" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="26" t="n"/>
-      <c r="B195" s="24" t="n"/>
-      <c r="C195" s="24" t="n"/>
-      <c r="D195" s="25" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="26" t="n"/>
-      <c r="B196" s="24" t="n"/>
-      <c r="C196" s="24" t="n"/>
-      <c r="D196" s="25" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="26" t="n"/>
-      <c r="B197" s="24" t="n"/>
-      <c r="C197" s="24" t="n"/>
-      <c r="D197" s="25" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="26" t="n"/>
-      <c r="B198" s="24" t="n"/>
-      <c r="C198" s="24" t="n"/>
-      <c r="D198" s="25" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="26" t="n"/>
-      <c r="B199" s="24" t="n"/>
-      <c r="C199" s="24" t="n"/>
-      <c r="D199" s="25" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="26" t="n"/>
-      <c r="B200" s="24" t="n"/>
-      <c r="C200" s="24" t="n"/>
-      <c r="D200" s="25" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="26" t="n"/>
-      <c r="B201" s="24" t="n"/>
-      <c r="C201" s="24" t="n"/>
-      <c r="D201" s="25" t="n"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="26" t="n"/>
-      <c r="B202" s="24" t="n"/>
-      <c r="C202" s="24" t="n"/>
-      <c r="D202" s="25" t="n"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="26" t="n"/>
-      <c r="B203" s="24" t="n"/>
-      <c r="C203" s="24" t="n"/>
-      <c r="D203" s="25" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="26" t="n"/>
-      <c r="B204" s="24" t="n"/>
-      <c r="C204" s="24" t="n"/>
-      <c r="D204" s="25" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="26" t="n"/>
-      <c r="B205" s="24" t="n"/>
-      <c r="C205" s="24" t="n"/>
-      <c r="D205" s="25" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="26" t="n"/>
-      <c r="B206" s="24" t="n"/>
-      <c r="C206" s="24" t="n"/>
-      <c r="D206" s="25" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="26" t="n"/>
-      <c r="B207" s="24" t="n"/>
-      <c r="C207" s="24" t="n"/>
-      <c r="D207" s="25" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="26" t="n"/>
-      <c r="B208" s="24" t="n"/>
-      <c r="C208" s="24" t="n"/>
-      <c r="D208" s="25" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="26" t="n"/>
-      <c r="B209" s="24" t="n"/>
-      <c r="C209" s="24" t="n"/>
-      <c r="D209" s="25" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="26" t="n"/>
-      <c r="B210" s="24" t="n"/>
-      <c r="C210" s="24" t="n"/>
-      <c r="D210" s="25" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="26" t="n"/>
-      <c r="B211" s="24" t="n"/>
-      <c r="C211" s="24" t="n"/>
-      <c r="D211" s="25" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="26" t="n"/>
-      <c r="B212" s="24" t="n"/>
-      <c r="C212" s="24" t="n"/>
-      <c r="D212" s="25" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="26" t="n"/>
-      <c r="B213" s="24" t="n"/>
-      <c r="C213" s="24" t="n"/>
-      <c r="D213" s="25" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="26" t="n"/>
-      <c r="B214" s="24" t="n"/>
-      <c r="C214" s="24" t="n"/>
-      <c r="D214" s="25" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="26" t="n"/>
-      <c r="B215" s="24" t="n"/>
-      <c r="C215" s="24" t="n"/>
-      <c r="D215" s="25" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="26" t="n"/>
-      <c r="B216" s="24" t="n"/>
-      <c r="C216" s="24" t="n"/>
-      <c r="D216" s="25" t="n"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="26" t="n"/>
-      <c r="B217" s="24" t="n"/>
-      <c r="C217" s="24" t="n"/>
-      <c r="D217" s="25" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="26" t="n"/>
-      <c r="B218" s="24" t="n"/>
-      <c r="C218" s="24" t="n"/>
-      <c r="D218" s="25" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="26" t="n"/>
-      <c r="B219" s="24" t="n"/>
-      <c r="C219" s="24" t="n"/>
-      <c r="D219" s="25" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="26" t="n"/>
-      <c r="B220" s="24" t="n"/>
-      <c r="C220" s="24" t="n"/>
-      <c r="D220" s="25" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="26" t="n"/>
-      <c r="B221" s="24" t="n"/>
-      <c r="C221" s="24" t="n"/>
-      <c r="D221" s="25" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="26" t="n"/>
-      <c r="B222" s="24" t="n"/>
-      <c r="C222" s="24" t="n"/>
-      <c r="D222" s="25" t="n"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="26" t="n"/>
-      <c r="B223" s="24" t="n"/>
-      <c r="C223" s="24" t="n"/>
-      <c r="D223" s="25" t="n"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="26" t="n"/>
-      <c r="B224" s="24" t="n"/>
-      <c r="C224" s="24" t="n"/>
-      <c r="D224" s="25" t="n"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="26" t="n"/>
-      <c r="B225" s="24" t="n"/>
-      <c r="C225" s="24" t="n"/>
-      <c r="D225" s="25" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="26" t="n"/>
-      <c r="B226" s="24" t="n"/>
-      <c r="C226" s="24" t="n"/>
-      <c r="D226" s="25" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="26" t="n"/>
-      <c r="B227" s="24" t="n"/>
-      <c r="C227" s="24" t="n"/>
-      <c r="D227" s="25" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="26" t="n"/>
-      <c r="B228" s="24" t="n"/>
-      <c r="C228" s="24" t="n"/>
-      <c r="D228" s="25" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="26" t="n"/>
-      <c r="B229" s="24" t="n"/>
-      <c r="C229" s="24" t="n"/>
-      <c r="D229" s="25" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="26" t="n"/>
-      <c r="B230" s="24" t="n"/>
-      <c r="C230" s="24" t="n"/>
-      <c r="D230" s="25" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="26" t="n"/>
-      <c r="B231" s="24" t="n"/>
-      <c r="C231" s="24" t="n"/>
-      <c r="D231" s="25" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="26" t="n"/>
-      <c r="B232" s="24" t="n"/>
-      <c r="C232" s="24" t="n"/>
-      <c r="D232" s="25" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="26" t="n"/>
-      <c r="B233" s="24" t="n"/>
-      <c r="C233" s="24" t="n"/>
-      <c r="D233" s="25" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="26" t="n"/>
-      <c r="B234" s="24" t="n"/>
-      <c r="C234" s="24" t="n"/>
-      <c r="D234" s="25" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="26" t="n"/>
-      <c r="B235" s="24" t="n"/>
-      <c r="C235" s="24" t="n"/>
-      <c r="D235" s="25" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="26" t="n"/>
-      <c r="B236" s="24" t="n"/>
-      <c r="C236" s="24" t="n"/>
-      <c r="D236" s="25" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="26" t="n"/>
-      <c r="B237" s="24" t="n"/>
-      <c r="C237" s="24" t="n"/>
-      <c r="D237" s="25" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="26" t="n"/>
-      <c r="B238" s="24" t="n"/>
-      <c r="C238" s="24" t="n"/>
-      <c r="D238" s="25" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="26" t="n"/>
-      <c r="B239" s="24" t="n"/>
-      <c r="C239" s="24" t="n"/>
-      <c r="D239" s="25" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="26" t="n"/>
-      <c r="B240" s="24" t="n"/>
-      <c r="C240" s="24" t="n"/>
-      <c r="D240" s="25" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="26" t="n"/>
-      <c r="B241" s="24" t="n"/>
-      <c r="C241" s="24" t="n"/>
-      <c r="D241" s="25" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="26" t="n"/>
-      <c r="B242" s="24" t="n"/>
-      <c r="C242" s="24" t="n"/>
-      <c r="D242" s="25" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="26" t="n"/>
-      <c r="B243" s="24" t="n"/>
-      <c r="C243" s="24" t="n"/>
-      <c r="D243" s="25" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="26" t="n"/>
-      <c r="B244" s="24" t="n"/>
-      <c r="C244" s="24" t="n"/>
-      <c r="D244" s="25" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="26" t="n"/>
-      <c r="B245" s="24" t="n"/>
-      <c r="C245" s="24" t="n"/>
-      <c r="D245" s="25" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="26" t="n"/>
-      <c r="B246" s="24" t="n"/>
-      <c r="C246" s="24" t="n"/>
-      <c r="D246" s="25" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="26" t="n"/>
-      <c r="B247" s="24" t="n"/>
-      <c r="C247" s="24" t="n"/>
-      <c r="D247" s="25" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="26" t="n"/>
-      <c r="B248" s="24" t="n"/>
-      <c r="C248" s="24" t="n"/>
-      <c r="D248" s="25" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="26" t="n"/>
-      <c r="B249" s="24" t="n"/>
-      <c r="C249" s="24" t="n"/>
-      <c r="D249" s="25" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="26" t="n"/>
-      <c r="B250" s="24" t="n"/>
-      <c r="C250" s="24" t="n"/>
-      <c r="D250" s="25" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="26" t="n"/>
-      <c r="B251" s="24" t="n"/>
-      <c r="C251" s="24" t="n"/>
-      <c r="D251" s="25" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="26" t="n"/>
-      <c r="B252" s="24" t="n"/>
-      <c r="C252" s="24" t="n"/>
-      <c r="D252" s="25" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="26" t="n"/>
-      <c r="B253" s="24" t="n"/>
-      <c r="C253" s="24" t="n"/>
-      <c r="D253" s="25" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="26" t="n"/>
-      <c r="B254" s="24" t="n"/>
-      <c r="C254" s="24" t="n"/>
-      <c r="D254" s="25" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="26" t="n"/>
-      <c r="B255" s="24" t="n"/>
-      <c r="C255" s="24" t="n"/>
-      <c r="D255" s="25" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="26" t="n"/>
-      <c r="B256" s="24" t="n"/>
-      <c r="C256" s="24" t="n"/>
-      <c r="D256" s="25" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="26" t="n"/>
-      <c r="B257" s="24" t="n"/>
-      <c r="C257" s="24" t="n"/>
-      <c r="D257" s="25" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="26" t="n"/>
-      <c r="B258" s="24" t="n"/>
-      <c r="C258" s="24" t="n"/>
-      <c r="D258" s="25" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="26" t="n"/>
-      <c r="B259" s="24" t="n"/>
-      <c r="C259" s="24" t="n"/>
-      <c r="D259" s="25" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="26" t="n"/>
-      <c r="B260" s="24" t="n"/>
-      <c r="C260" s="24" t="n"/>
-      <c r="D260" s="25" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="26" t="n"/>
-      <c r="B261" s="24" t="n"/>
-      <c r="C261" s="24" t="n"/>
-      <c r="D261" s="25" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="26" t="n"/>
-      <c r="B262" s="24" t="n"/>
-      <c r="C262" s="24" t="n"/>
-      <c r="D262" s="25" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="26" t="n"/>
-      <c r="B263" s="24" t="n"/>
-      <c r="C263" s="24" t="n"/>
-      <c r="D263" s="25" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="26" t="n"/>
-      <c r="B264" s="24" t="n"/>
-      <c r="C264" s="24" t="n"/>
-      <c r="D264" s="25" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="26" t="n"/>
-      <c r="B265" s="24" t="n"/>
-      <c r="C265" s="24" t="n"/>
-      <c r="D265" s="25" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="26" t="n"/>
-      <c r="B266" s="24" t="n"/>
-      <c r="C266" s="24" t="n"/>
-      <c r="D266" s="25" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="26" t="n"/>
-      <c r="B267" s="24" t="n"/>
-      <c r="C267" s="24" t="n"/>
-      <c r="D267" s="25" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="26" t="n"/>
-      <c r="B268" s="24" t="n"/>
-      <c r="C268" s="24" t="n"/>
-      <c r="D268" s="25" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="26" t="n"/>
-      <c r="B269" s="24" t="n"/>
-      <c r="C269" s="24" t="n"/>
-      <c r="D269" s="25" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="26" t="n"/>
-      <c r="B270" s="24" t="n"/>
-      <c r="C270" s="24" t="n"/>
-      <c r="D270" s="25" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="26" t="n"/>
-      <c r="B271" s="24" t="n"/>
-      <c r="C271" s="24" t="n"/>
-      <c r="D271" s="25" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="26" t="n"/>
-      <c r="B272" s="24" t="n"/>
-      <c r="C272" s="24" t="n"/>
-      <c r="D272" s="25" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="26" t="n"/>
-      <c r="B273" s="24" t="n"/>
-      <c r="C273" s="24" t="n"/>
-      <c r="D273" s="25" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="26" t="n"/>
-      <c r="B274" s="24" t="n"/>
-      <c r="C274" s="24" t="n"/>
-      <c r="D274" s="25" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="26" t="n"/>
-      <c r="B275" s="24" t="n"/>
-      <c r="C275" s="24" t="n"/>
-      <c r="D275" s="25" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="26" t="n"/>
-      <c r="B276" s="24" t="n"/>
-      <c r="C276" s="24" t="n"/>
-      <c r="D276" s="25" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="26" t="n"/>
-      <c r="B277" s="24" t="n"/>
-      <c r="C277" s="24" t="n"/>
-      <c r="D277" s="25" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="26" t="n"/>
-      <c r="B278" s="24" t="n"/>
-      <c r="C278" s="24" t="n"/>
-      <c r="D278" s="25" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="26" t="n"/>
-      <c r="B279" s="24" t="n"/>
-      <c r="C279" s="24" t="n"/>
-      <c r="D279" s="25" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="26" t="n"/>
-      <c r="B280" s="24" t="n"/>
-      <c r="C280" s="24" t="n"/>
-      <c r="D280" s="25" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="26" t="n"/>
-      <c r="B281" s="24" t="n"/>
-      <c r="C281" s="24" t="n"/>
-      <c r="D281" s="25" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="26" t="n"/>
-      <c r="B282" s="24" t="n"/>
-      <c r="C282" s="24" t="n"/>
-      <c r="D282" s="25" t="n"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="26" t="n"/>
-      <c r="B283" s="24" t="n"/>
-      <c r="C283" s="24" t="n"/>
-      <c r="D283" s="25" t="n"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="26" t="n"/>
-      <c r="B284" s="24" t="n"/>
-      <c r="C284" s="24" t="n"/>
-      <c r="D284" s="25" t="n"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="26" t="n"/>
-      <c r="B285" s="24" t="n"/>
-      <c r="C285" s="24" t="n"/>
-      <c r="D285" s="25" t="n"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="26" t="n"/>
-      <c r="B286" s="24" t="n"/>
-      <c r="C286" s="24" t="n"/>
-      <c r="D286" s="25" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="26" t="n"/>
-      <c r="B287" s="24" t="n"/>
-      <c r="C287" s="24" t="n"/>
-      <c r="D287" s="25" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="26" t="n"/>
-      <c r="B288" s="24" t="n"/>
-      <c r="C288" s="24" t="n"/>
-      <c r="D288" s="25" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="26" t="n"/>
-      <c r="B289" s="24" t="n"/>
-      <c r="C289" s="24" t="n"/>
-      <c r="D289" s="25" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="26" t="n"/>
-      <c r="B290" s="24" t="n"/>
-      <c r="C290" s="24" t="n"/>
-      <c r="D290" s="25" t="n"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="26" t="n"/>
-      <c r="B291" s="24" t="n"/>
-      <c r="C291" s="24" t="n"/>
-      <c r="D291" s="25" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="26" t="n"/>
-      <c r="B292" s="24" t="n"/>
-      <c r="C292" s="24" t="n"/>
-      <c r="D292" s="25" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="26" t="n"/>
-      <c r="B293" s="24" t="n"/>
-      <c r="C293" s="24" t="n"/>
-      <c r="D293" s="25" t="n"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="26" t="n"/>
-      <c r="B294" s="24" t="n"/>
-      <c r="C294" s="24" t="n"/>
-      <c r="D294" s="25" t="n"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="26" t="n"/>
-      <c r="B295" s="24" t="n"/>
-      <c r="C295" s="24" t="n"/>
-      <c r="D295" s="25" t="n"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="26" t="n"/>
-      <c r="B296" s="24" t="n"/>
-      <c r="C296" s="24" t="n"/>
-      <c r="D296" s="25" t="n"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="26" t="n"/>
-      <c r="B297" s="24" t="n"/>
-      <c r="C297" s="24" t="n"/>
-      <c r="D297" s="25" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="26" t="n"/>
-      <c r="B298" s="24" t="n"/>
-      <c r="C298" s="24" t="n"/>
-      <c r="D298" s="25" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="26" t="n"/>
-      <c r="B299" s="24" t="n"/>
-      <c r="C299" s="24" t="n"/>
-      <c r="D299" s="25" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="26" t="n"/>
-      <c r="B300" s="24" t="n"/>
-      <c r="C300" s="24" t="n"/>
-      <c r="D300" s="25" t="n"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="26" t="n"/>
-      <c r="B301" s="24" t="n"/>
-      <c r="C301" s="24" t="n"/>
-      <c r="D301" s="25" t="n"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="26" t="n"/>
-      <c r="B302" s="24" t="n"/>
-      <c r="C302" s="24" t="n"/>
-      <c r="D302" s="25" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="26" t="n"/>
-      <c r="B303" s="24" t="n"/>
-      <c r="C303" s="24" t="n"/>
-      <c r="D303" s="25" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="26" t="n"/>
-      <c r="B304" s="24" t="n"/>
-      <c r="C304" s="24" t="n"/>
-      <c r="D304" s="25" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="26" t="n"/>
-      <c r="B305" s="24" t="n"/>
-      <c r="C305" s="24" t="n"/>
-      <c r="D305" s="25" t="n"/>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <autoFilter ref="A5:D305"/>
+  <autoFilter ref="A5:D125"/>
   <mergeCells count="1">
     <mergeCell ref="A3:D3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6:B305" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B6:B125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=SALES!$A$6:$A$17</formula1>
     </dataValidation>
   </dataValidations>
@@ -4312,7 +3264,7 @@
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>IF($A6="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A6,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A6="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A6,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E6" s="29">
@@ -4358,7 +3310,7 @@
         <v/>
       </c>
       <c r="D7" s="28">
-        <f>IF($A7="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A7,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A7="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A7,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E7" s="29">
@@ -4404,7 +3356,7 @@
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>IF($A8="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A8,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A8="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A8,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E8" s="29">
@@ -4450,7 +3402,7 @@
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>IF($A9="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A9,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A9="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A9,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E9" s="29">
@@ -4496,7 +3448,7 @@
         <v/>
       </c>
       <c r="D10" s="28">
-        <f>IF($A10="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A10,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A10="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A10,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E10" s="29">
@@ -4542,7 +3494,7 @@
         <v/>
       </c>
       <c r="D11" s="28">
-        <f>IF($A11="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A11,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A11="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A11,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E11" s="29">
@@ -4588,7 +3540,7 @@
         <v/>
       </c>
       <c r="D12" s="28">
-        <f>IF($A12="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A12,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A12="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A12,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E12" s="29">
@@ -4634,7 +3586,7 @@
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>IF($A13="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A13,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A13="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A13,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E13" s="29">
@@ -4680,7 +3632,7 @@
         <v/>
       </c>
       <c r="D14" s="28">
-        <f>IF($A14="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A14,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A14="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A14,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E14" s="29">
@@ -4726,7 +3678,7 @@
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>IF($A15="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A15,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A15="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A15,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E15" s="29">
@@ -4772,7 +3724,7 @@
         <v/>
       </c>
       <c r="D16" s="28">
-        <f>IF($A16="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A16,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A16="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A16,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E16" s="29">
@@ -4818,7 +3770,7 @@
         <v/>
       </c>
       <c r="D17" s="28">
-        <f>IF($A17="","",SUMIFS(PENJUALAN!$D$6:$D$305,PENJUALAN!$B$6:$B$305,$A17,PENJUALAN!$A$6:$A$305,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$305,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
+        <f>IF($A17="","",SUMIFS(PENJUALAN!$D$6:$D$125,PENJUALAN!$B$6:$B$125,$A17,PENJUALAN!$A$6:$A$125,"&gt;="&amp;DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),PENJUALAN!$A$6:$A$125,"&lt;"&amp;EDATE(DATE(PARAMETER!$C$5,PARAMETER!$C$6,1),1)))</f>
         <v/>
       </c>
       <c r="E17" s="29">
@@ -4900,4 +3852,202 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>REKAP TAHUNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Matriks pencapaian dan komisi per sales per bulan, plus total tahun berjalan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>SLIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Slip komisi satu sales untuk bulan terpilih, siap dicetak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Peringkat 3 teratas, total realisasi vs target, dan grafik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>